--- a/reports/devops-juniors-israel-2026-W26.xlsx
+++ b/reports/devops-juniors-israel-2026-W26.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="388">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-22T12:23:56</t>
+    <t xml:space="preserve">2026-06-23T10:01:17</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -100,12 +100,12 @@
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
-  </si>
-  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -184,802 +184,874 @@
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
+    <t xml:space="preserve">HPC &amp; Linux Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-linux-systems-engineer-at-ben-gurion-university-of-the-negev-4427607653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Engineer (DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-engineer-devops-at-teads-4431209410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Specialist</t>
   </si>
   <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
+    <t xml:space="preserve">Anecdotes</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infrastructure &amp; Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Squadron Israel - Hatayeset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-technical-support-specialist-at-the-squadron-israel-hatayeset-4421938671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Product Operations – Part-Time Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-product-operations-%E2%80%93-part-time-student-at-finout-4427681349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aristocrat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-aristocrat-4413900417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-specialist-at-log-on-software-4425797474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zensar Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allied Worldwide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - JB-651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-riverside-4409620033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategy Analyst Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (24892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4427354216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-at-abra-4432200564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412563583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-monday-com-4430722480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-01</t>
   </si>
   <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-specialist-at-log-on-software-4425797474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allied Worldwide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - JB-651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist - JB-594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-jb-594-at-pwc-israel-4429922813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (Temporary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONE Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-one-technologies-4432205195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk / System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egoz Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ayelet HaShahar, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-system-at-egoz-systems-4431679966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4425818718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4427419615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beth-El Industries Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wobi Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-junior-at-wobi-ltd-4419670684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support/ Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-help-desk-at-unilink-ltd-4431703188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk - 239819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-26</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux Software Embedded Engineer (Junior position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDA Space</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-software-embedded-engineer-junior-position-at-mda-space-4422723139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strategy Analyst Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (24892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4427354216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+    <t xml:space="preserve">Help Desk Technician - junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part time )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-team-leader-at-calanit-by-one-4431666655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-comblack-4431707095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סטודנט/ית למחלקת התכנון</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safed, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%A1%D7%98%D7%95%D7%93%D7%A0%D7%98-%D7%99%D7%AA-%D7%9C%D7%9E%D7%97%D7%9C%D7%A7%D7%AA-%D7%94%D7%AA%D7%9B%D7%A0%D7%95%D7%9F-at-unilever-4426489234</t>
   </si>
   <si>
     <t xml:space="preserve">Systems Engineering Student</t>
   </si>
   <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Algorithm System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/algorithm-system-engineer-at-elbit-systems-israel-4412906510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist - JB-594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-jb-594-at-pwc-israel-4429922813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (Temporary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk / System</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egoz Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ayelet HaShahar, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-system-at-egoz-systems-4431679966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4425818718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desktop Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pathway Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toronto, Toronto, Ontario, Canada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-desktop-support-technician-pathway-communications-1133710</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4427419615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beth-El Industries Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wobi Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-junior-at-wobi-ltd-4419670684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk - 239819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician - junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excis Compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4429959640</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zoho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part time )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-south-apac-sea-anz-ind-subcont-4427828397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-operator-at-tata-consultancy-services-4427424594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סטודנט/ית למחלקת התכנון</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilever</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Safed, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%A1%D7%98%D7%95%D7%93%D7%A0%D7%98-%D7%99%D7%AA-%D7%9C%D7%9E%D7%97%D7%9C%D7%A7%D7%AA-%D7%94%D7%AA%D7%9B%D7%A0%D7%95%D7%9F-at-unilever-4426489234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4417232078</t>
   </si>
   <si>
     <t xml:space="preserve">No Experience</t>
@@ -1012,25 +1084,31 @@
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">Linux</t>
@@ -1039,48 +1117,36 @@
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform/IaC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
+  </si>
+  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
     <t xml:space="preserve">Count</t>
   </si>
   <si>
@@ -1096,10 +1162,10 @@
     <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
   </si>
   <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -1236,7 +1302,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -1244,7 +1310,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1252,7 +1318,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -1260,7 +1326,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>302</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -1342,7 +1408,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22">
@@ -1358,7 +1424,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -1392,7 +1458,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29">
@@ -1408,7 +1474,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1420,8 +1486,8 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
-    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="43" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -1540,10 +1606,10 @@
         <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>59</v>
@@ -1563,31 +1629,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F5" s="3">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -1595,31 +1661,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -1627,28 +1693,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="E7" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F7" s="3">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>49</v>
@@ -1659,31 +1725,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -1691,31 +1757,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3">
         <v>44</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -1723,13 +1789,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>25</v>
@@ -1738,16 +1804,16 @@
         <v>44</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
@@ -1755,31 +1821,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F11" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -1787,31 +1853,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -1819,31 +1885,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14">
@@ -1851,31 +1917,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F14" s="3">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>111</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -1883,31 +1949,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16">
@@ -1915,19 +1981,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>120</v>
@@ -1939,7 +2005,7 @@
         <v>121</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17">
@@ -1947,31 +2013,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>58</v>
+        <v>125</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>65</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18">
@@ -1979,31 +2045,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>126</v>
+        <v>50</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19">
@@ -2011,31 +2077,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>49</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20">
@@ -2043,31 +2109,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21">
@@ -2075,31 +2141,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22">
@@ -2107,31 +2173,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23">
@@ -2139,31 +2205,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>149</v>
+        <v>100</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>49</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24">
@@ -2171,31 +2237,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>157</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25">
@@ -2203,31 +2269,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>163</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26">
@@ -2235,31 +2301,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2298,7 +2364,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2312,7 +2378,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>36</v>
@@ -2327,22 +2393,22 @@
         <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2">
@@ -2365,7 +2431,7 @@
         <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2377,7 +2443,7 @@
         <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -2400,7 +2466,7 @@
         <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2412,7 +2478,7 @@
         <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -2426,16 +2492,16 @@
         <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2447,193 +2513,193 @@
         <v>61</v>
       </c>
       <c r="K4" s="3">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E5" s="3">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K5" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="K6" s="3">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="D7" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E7" s="3">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>49</v>
       </c>
       <c r="K7" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="K8" s="3">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3">
         <v>44</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K9" s="3">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>25</v>
@@ -2642,220 +2708,220 @@
         <v>44</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="K10" s="3">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K11" s="3">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" s="3">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="K12" s="3">
-        <v>11</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K13" s="3">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E14" s="3">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="K15" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>120</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
@@ -2864,418 +2930,418 @@
         <v>121</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="K16" s="3">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>58</v>
+        <v>125</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="K17" s="3">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>126</v>
+        <v>50</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K18" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>49</v>
+        <v>138</v>
       </c>
       <c r="K19" s="3">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="K20" s="3">
-        <v>4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="K21" s="3">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="3">
+        <v>27</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K22" s="3">
         <v>23</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="K22" s="3">
-        <v>27</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>149</v>
+        <v>100</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E23" s="3">
+        <v>27</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="K23" s="3">
         <v>20</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K23" s="3">
-        <v>38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>157</v>
+        <v>49</v>
       </c>
       <c r="K24" s="3">
-        <v>12</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E25" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="K25" s="3">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="K26" s="3">
-        <v>4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>49</v>
       </c>
       <c r="K27" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>179</v>
+        <v>68</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>181</v>
+        <v>70</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>182</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
@@ -3284,10 +3350,10 @@
         <v>183</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="K28" s="3">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29">
@@ -3295,290 +3361,290 @@
         <v>184</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E29" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K29" s="3">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="K30" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E31" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="K31" s="3">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E32" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="K32" s="3">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E33" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>55</v>
+        <v>209</v>
       </c>
       <c r="K33" s="3">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>136</v>
+        <v>205</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>58</v>
+        <v>211</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E34" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>65</v>
+        <v>209</v>
       </c>
       <c r="K34" s="3">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>205</v>
+        <v>93</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>207</v>
+        <v>70</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="K35" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E36" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>111</v>
+        <v>220</v>
       </c>
       <c r="K36" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
@@ -3587,33 +3653,33 @@
         <v>10</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>221</v>
+        <v>55</v>
       </c>
       <c r="K37" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>56</v>
+        <v>226</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
@@ -3622,33 +3688,33 @@
         <v>10</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="K38" s="3">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>225</v>
+        <v>164</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>226</v>
+        <v>70</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
@@ -3657,33 +3723,33 @@
         <v>10</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>228</v>
+        <v>73</v>
       </c>
       <c r="K39" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
@@ -3692,278 +3758,278 @@
         <v>10</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="K40" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>210</v>
+        <v>67</v>
       </c>
       <c r="K41" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E42" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="K42" s="3">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>244</v>
+        <v>68</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>132</v>
+        <v>247</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>247</v>
+        <v>55</v>
       </c>
       <c r="K43" s="3">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44" s="3">
+        <v>10</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E44" s="3">
-        <v>6</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="G44" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>210</v>
+        <v>253</v>
       </c>
       <c r="K44" s="3">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>234</v>
+        <v>61</v>
       </c>
       <c r="K45" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>258</v>
+        <v>100</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E46" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>146</v>
+        <v>237</v>
       </c>
       <c r="K46" s="3">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E47" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>265</v>
+        <v>55</v>
       </c>
       <c r="K47" s="3">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>267</v>
+        <v>160</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
@@ -3975,7 +4041,7 @@
         <v>268</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>31</v>
@@ -3984,10 +4050,10 @@
         <v>269</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="K48" s="3">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
@@ -3998,7 +4064,7 @@
         <v>271</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>272</v>
+        <v>141</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
@@ -4007,10 +4073,10 @@
         <v>6</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>31</v>
@@ -4019,10 +4085,10 @@
         <v>273</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>55</v>
+        <v>237</v>
       </c>
       <c r="K49" s="3">
-        <v>29</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50">
@@ -4033,7 +4099,7 @@
         <v>275</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>97</v>
+        <v>276</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
@@ -4042,33 +4108,33 @@
         <v>6</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K50" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>280</v>
+        <v>105</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
@@ -4077,10 +4143,10 @@
         <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>31</v>
@@ -4089,10 +4155,10 @@
         <v>281</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K51" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -4103,7 +4169,7 @@
         <v>283</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>86</v>
+        <v>284</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
@@ -4112,10 +4178,10 @@
         <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>31</v>
@@ -4124,21 +4190,21 @@
         <v>285</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>228</v>
+        <v>286</v>
       </c>
       <c r="K52" s="3">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>58</v>
+        <v>289</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4147,370 +4213,580 @@
         <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>245</v>
+        <v>290</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K53" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>292</v>
+        <v>70</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E54" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>221</v>
+        <v>297</v>
       </c>
       <c r="K54" s="3">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>295</v>
+        <v>238</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E55" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>298</v>
+        <v>268</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
       <c r="K55" s="3">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E56" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>302</v>
+        <v>153</v>
       </c>
       <c r="K56" s="3">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>44</v>
+        <v>304</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>292</v>
+        <v>100</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E57" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="K57" s="3">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E58" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>306</v>
+        <v>268</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>187</v>
+        <v>311</v>
       </c>
       <c r="K58" s="3">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E59" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>116</v>
+        <v>253</v>
       </c>
       <c r="K59" s="3">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>314</v>
+        <v>150</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E60" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>293</v>
+        <v>319</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="K60" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>316</v>
+        <v>44</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
-      </c>
-      <c r="F61" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>315</v>
+      </c>
       <c r="G61" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>302</v>
+        <v>55</v>
       </c>
       <c r="K61" s="3">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>180</v>
+        <v>323</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>185</v>
+        <v>100</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>324</v>
+      </c>
       <c r="G62" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>187</v>
+        <v>297</v>
       </c>
       <c r="K62" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C63" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E63" s="3">
+        <v>3</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="K63" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E64" s="3">
+        <v>3</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="K64" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E65" s="3">
+        <v>3</v>
+      </c>
+      <c r="F65" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="G65" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E63" s="3">
+      <c r="E67" s="3">
         <v>0</v>
       </c>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="H63" s="3" t="s">
+      <c r="F67" s="3"/>
+      <c r="G67" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="K67" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E68" s="3">
+        <v>0</v>
+      </c>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E69" s="3">
+        <v>0</v>
+      </c>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H69" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I63" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K63" s="3">
-        <v>0</v>
+      <c r="I69" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="K69" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K63"/>
+  <autoFilter ref="A1:K69"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4574,6 +4850,12 @@
     <hyperlink ref="I61" r:id="rId60"/>
     <hyperlink ref="I62" r:id="rId61"/>
     <hyperlink ref="I63" r:id="rId62"/>
+    <hyperlink ref="I64" r:id="rId63"/>
+    <hyperlink ref="I65" r:id="rId64"/>
+    <hyperlink ref="I66" r:id="rId65"/>
+    <hyperlink ref="I67" r:id="rId66"/>
+    <hyperlink ref="I68" r:id="rId67"/>
+    <hyperlink ref="I69" r:id="rId68"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4581,11 +4863,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="46" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -4604,10 +4886,10 @@
         <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>43</v>
@@ -4615,77 +4897,197 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2" s="3">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>212</v>
+        <v>160</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D3" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>322</v>
+        <v>226</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>323</v>
+        <v>227</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="3">
+        <v>10</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3">
+        <v>6</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D9" s="3">
         <v>0</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>111</v>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G9"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
+    <hyperlink ref="F5" r:id="rId4"/>
+    <hyperlink ref="F6" r:id="rId5"/>
+    <hyperlink ref="F7" r:id="rId6"/>
+    <hyperlink ref="F8" r:id="rId7"/>
+    <hyperlink ref="F9" r:id="rId8"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4700,178 +5102,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>326</v>
+        <v>350</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>328</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="B2" s="3">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>329</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>330</v>
+        <v>354</v>
       </c>
       <c r="B3" s="3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>331</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>306</v>
+        <v>356</v>
       </c>
       <c r="B4" s="3">
         <v>21</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>332</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>334</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>335</v>
+        <v>359</v>
       </c>
       <c r="B6" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>336</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>182</v>
+        <v>319</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>337</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>298</v>
+        <v>207</v>
       </c>
       <c r="B8" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>338</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>339</v>
+        <v>363</v>
       </c>
       <c r="B9" s="3">
         <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>340</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="B10" s="3">
         <v>10</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="B11" s="3">
         <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>344</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="B13" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>349</v>
+        <v>202</v>
       </c>
       <c r="B14" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="B16" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -4891,10 +5293,10 @@
         <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2">
@@ -4902,10 +5304,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3">
@@ -4916,7 +5318,7 @@
         <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4">
@@ -4924,10 +5326,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
     </row>
     <row r="5">
@@ -4938,7 +5340,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6">
@@ -4949,7 +5351,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -4970,13 +5372,13 @@
         <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2">
@@ -4987,7 +5389,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4996,10 +5398,10 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -5008,10 +5410,10 @@
         <v>33</v>
       </c>
       <c r="B4" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W26.xlsx
+++ b/reports/devops-juniors-israel-2026-W26.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="408">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-23T10:01:17</t>
+    <t xml:space="preserve">2026-06-24T09:49:49</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -100,9 +100,6 @@
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
@@ -184,967 +181,1033 @@
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
-    <t xml:space="preserve">HPC &amp; Linux Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-linux-systems-engineer-at-ben-gurion-university-of-the-negev-4427607653</t>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Inclined Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-inclined-systems-engineer-at-sb0-4429860196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Candex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-candex-4410031859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-14</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Cloud Engineer (DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4432227642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aristocrat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-aristocrat-4413900417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allied Worldwide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - JB-651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (35684)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-35684-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4432248548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-at-nebius-4425236974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk &amp; IT Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-it-administrator-at-mize-4425999700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategy Analyst Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (24892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4427354216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Eng.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultra Information Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-eng-at-ultra-information-solutions-4412395476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cross-river-4408813327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algorithm System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/algorithm-system-engineer-at-elbit-systems-israel-4412906510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Data</t>
   </si>
   <si>
     <t xml:space="preserve">Netanya, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-engineer-devops-at-teads-4431209410</t>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONE Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-one-technologies-4432205195</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-23</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infrastructure &amp; Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Squadron Israel - Hatayeset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-technical-support-specialist-at-the-squadron-israel-hatayeset-4421938671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Product Operations – Part-Time Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-product-operations-%E2%80%93-part-time-student-at-finout-4427681349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aristocrat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-aristocrat-4413900417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
+    <t xml:space="preserve">Helpdesk / System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egoz Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ayelet HaShahar, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-system-at-egoz-systems-4431679966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist - JB-594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-jb-594-at-pwc-israel-4429922813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (Temporary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4425818718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support – Power Quality Meters &amp; Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elspec Engineering ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-power-quality-meters-software-at-elspec-engineering-ltd-4413397801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4427419615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beth-El Industries Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician - junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4429856103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk - 239819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wobi Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-junior-at-wobi-ltd-4419670684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part time )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-09</t>
   </si>
   <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-specialist-at-log-on-software-4425797474</t>
+    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-operator-at-tata-consultancy-services-4427424594</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-16</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zensar Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allied Worldwide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - JB-651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-riverside-4409620033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strategy Analyst Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (24892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4427354216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-at-abra-4432200564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412563583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-monday-com-4430722480</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist - JB-594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-jb-594-at-pwc-israel-4429922813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (Temporary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONE Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-one-technologies-4432205195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk / System</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egoz Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ayelet HaShahar, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-system-at-egoz-systems-4431679966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4425818718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4427419615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beth-El Industries Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wobi Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-junior-at-wobi-ltd-4419670684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support/ Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-help-desk-at-unilink-ltd-4431703188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk - 239819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician - junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zoho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part time )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4431366669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 2 Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tier-2-technician-at-solaredge-technologies-4431252112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סטודנט/ית למחלקת התכנון</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safed, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%A1%D7%98%D7%95%D7%93%D7%A0%D7%98-%D7%99%D7%AA-%D7%9C%D7%9E%D7%97%D7%9C%D7%A7%D7%AA-%D7%94%D7%AA%D7%9B%D7%A0%D7%95%D7%9F-at-unilever-4426489234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Experience</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG&amp;amp;T Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Dorado,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-no-experience-rgampt-solutions-1133829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-team-leader-at-calanit-by-one-4431666655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-comblack-4431707095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סטודנט/ית למחלקת התכנון</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilever</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Safed, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%A1%D7%98%D7%95%D7%93%D7%A0%D7%98-%D7%99%D7%AA-%D7%9C%D7%9E%D7%97%D7%9C%D7%A7%D7%AA-%D7%94%D7%AA%D7%9B%D7%A0%D7%95%D7%9F-at-unilever-4426489234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4417232078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Experience</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RG&amp;amp;T Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Dorado,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-no-experience-rgampt-solutions-1133829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1160,9 +1223,6 @@
   </si>
   <si>
     <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
   </si>
   <si>
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
@@ -1302,7 +1362,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
@@ -1310,7 +1370,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -1318,7 +1378,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -1326,7 +1386,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>310</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1408,7 +1468,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22">
@@ -1416,7 +1476,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -1424,7 +1484,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1436,29 +1496,29 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3"/>
       <c r="B26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="3"/>
+      <c r="B27" s="3">
+        <v>67</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -1466,14 +1526,6 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B30" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1486,8 +1538,8 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
-    <col min="4" max="4" width="43" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -1498,34 +1550,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -1533,13 +1585,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>25</v>
@@ -1548,16 +1600,16 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -1565,13 +1617,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>26</v>
@@ -1580,16 +1632,16 @@
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -1597,31 +1649,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="3">
+        <v>88</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="3">
-        <v>92</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -1629,31 +1681,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="3">
+        <v>80</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="3">
-        <v>84</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -1661,31 +1713,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="3">
+        <v>76</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="3">
-        <v>68</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -1693,31 +1745,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3">
         <v>57</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -1725,31 +1777,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="3">
+        <v>52</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="3">
-        <v>47</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9">
@@ -1757,31 +1809,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="E9" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F9" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>84</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>85</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -1789,31 +1841,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="3">
+        <v>47</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="3">
-        <v>44</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="11">
@@ -1821,31 +1873,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="3">
+        <v>47</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="3">
-        <v>44</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -1853,31 +1905,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="3">
+        <v>47</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="3">
-        <v>44</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -1885,31 +1937,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14">
@@ -1917,31 +1969,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="3">
+        <v>44</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="3">
-        <v>35</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="J14" s="3" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -1949,31 +2001,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="3">
+        <v>44</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" s="3">
-        <v>32</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="16">
@@ -1981,31 +2033,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17">
@@ -2013,31 +2065,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="3">
+        <v>40</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="3">
-        <v>30</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18">
@@ -2045,31 +2097,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>130</v>
+        <v>69</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>133</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
@@ -2077,31 +2129,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20">
@@ -2109,31 +2161,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21">
@@ -2141,31 +2193,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>70</v>
+        <v>139</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22">
@@ -2173,31 +2225,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>148</v>
+        <v>49</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23">
@@ -2205,31 +2257,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24">
@@ -2237,31 +2289,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>141</v>
+        <v>69</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="3">
         <v>27</v>
       </c>
-      <c r="F24" s="3">
-        <v>26</v>
-      </c>
       <c r="G24" s="3" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>49</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25">
@@ -2269,31 +2321,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>73</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26">
@@ -2301,31 +2353,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>141</v>
+        <v>63</v>
       </c>
       <c r="E26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="3">
         <v>26</v>
       </c>
-      <c r="F26" s="3">
-        <v>24</v>
-      </c>
       <c r="G26" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2364,7 +2416,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2378,48 +2430,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>25</v>
@@ -2428,33 +2480,33 @@
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="K2" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>26</v>
@@ -2463,89 +2515,89 @@
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="J3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K3" s="3">
         <v>31</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K3" s="3">
-        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="3">
+        <v>88</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K4" s="3">
         <v>26</v>
-      </c>
-      <c r="E4" s="3">
-        <v>92</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="K4" s="3">
-        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="3">
+        <v>80</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="3">
-        <v>84</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="K5" s="3">
         <v>0</v>
@@ -2553,1343 +2605,1343 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="3">
+        <v>76</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="3">
-        <v>68</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="K6" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7" s="3">
         <v>57</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K7" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="3">
+        <v>52</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="3">
-        <v>47</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="K8" s="3">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="D9" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>84</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>85</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="K9" s="3">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="3">
+        <v>47</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="3">
-        <v>44</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="K10" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="3">
+        <v>47</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="3">
-        <v>44</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="K11" s="3">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3">
+        <v>47</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="3">
-        <v>44</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="K12" s="3">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="K13" s="3">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="3">
+        <v>44</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="3">
-        <v>35</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="J14" s="3" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="K14" s="3">
-        <v>9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="3">
+        <v>44</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="3">
-        <v>32</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="K15" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="K16" s="3">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="3">
+        <v>40</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="3">
-        <v>30</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="K17" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>130</v>
+        <v>69</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>133</v>
+        <v>66</v>
       </c>
       <c r="K18" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="K19" s="3">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="K20" s="3">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>70</v>
+        <v>139</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="K21" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>148</v>
+        <v>49</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="K22" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E23" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="K23" s="3">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>141</v>
+        <v>69</v>
       </c>
       <c r="D24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="3">
         <v>27</v>
       </c>
-      <c r="E24" s="3">
-        <v>26</v>
-      </c>
       <c r="F24" s="3" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>49</v>
+        <v>155</v>
       </c>
       <c r="K24" s="3">
-        <v>39</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="K25" s="3">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>141</v>
+        <v>63</v>
       </c>
       <c r="D26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="3">
         <v>26</v>
       </c>
-      <c r="E26" s="3">
-        <v>24</v>
-      </c>
       <c r="F26" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K26" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>178</v>
+        <v>107</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>49</v>
+        <v>155</v>
       </c>
       <c r="K27" s="3">
-        <v>39</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="K28" s="3">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>189</v>
+        <v>48</v>
       </c>
       <c r="K29" s="3">
-        <v>19</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>192</v>
+        <v>63</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E30" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="K30" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="K31" s="3">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>201</v>
+        <v>69</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>67</v>
+        <v>196</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E33" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="K33" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>211</v>
-      </c>
       <c r="D34" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F34" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>212</v>
-      </c>
       <c r="J34" s="3" t="s">
-        <v>209</v>
+        <v>155</v>
       </c>
       <c r="K34" s="3">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>93</v>
+        <v>208</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>216</v>
+        <v>48</v>
       </c>
       <c r="K35" s="3">
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>195</v>
+        <v>119</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E36" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>220</v>
+        <v>48</v>
       </c>
       <c r="K36" s="3">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>223</v>
+        <v>189</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E37" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K37" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>70</v>
+        <v>222</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E38" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>67</v>
+        <v>224</v>
       </c>
       <c r="K38" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>230</v>
+        <v>55</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>164</v>
+        <v>225</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>70</v>
+        <v>205</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="K39" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="3">
+        <v>13</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="J40" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E40" s="3">
-        <v>10</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>237</v>
-      </c>
       <c r="K40" s="3">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>105</v>
+        <v>235</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>67</v>
+        <v>237</v>
       </c>
       <c r="K41" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E42" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>245</v>
+        <v>219</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K42" s="3">
         <v>31</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="K42" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E43" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>248</v>
+        <v>219</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="K43" s="3">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>64</v>
+        <v>244</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
@@ -3898,33 +3950,33 @@
         <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>253</v>
+        <v>54</v>
       </c>
       <c r="K44" s="3">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
@@ -3933,383 +3985,383 @@
         <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>61</v>
+        <v>252</v>
       </c>
       <c r="K45" s="3">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="K46" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" s="3">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I47" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E47" s="3">
-        <v>8</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>266</v>
-      </c>
       <c r="J47" s="3" t="s">
-        <v>55</v>
+        <v>146</v>
       </c>
       <c r="K47" s="3">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>160</v>
+        <v>264</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>141</v>
+        <v>69</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E48" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>209</v>
+        <v>257</v>
       </c>
       <c r="K48" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>271</v>
+        <v>172</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>141</v>
+        <v>69</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E49" s="3">
+        <v>10</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K49" s="3">
         <v>6</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K49" s="3">
-        <v>8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>272</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="K50" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>279</v>
+        <v>81</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H51" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K51" s="3">
         <v>31</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="K51" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E52" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>286</v>
+        <v>113</v>
       </c>
       <c r="K52" s="3">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E53" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>292</v>
+        <v>224</v>
       </c>
       <c r="K53" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E54" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="K54" s="3">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>238</v>
+        <v>289</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E55" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H55" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K55" s="3">
         <v>31</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K55" s="3">
-        <v>30</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>301</v>
+        <v>253</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>115</v>
+        <v>295</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
@@ -4318,33 +4370,33 @@
         <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H56" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K56" s="3">
         <v>31</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="K56" s="3">
-        <v>23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
@@ -4353,33 +4405,33 @@
         <v>6</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>61</v>
+        <v>303</v>
       </c>
       <c r="K57" s="3">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>308</v>
+        <v>95</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>309</v>
+        <v>162</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>25</v>
@@ -4388,124 +4440,124 @@
         <v>6</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>311</v>
+        <v>160</v>
       </c>
       <c r="K58" s="3">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>314</v>
+        <v>91</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E59" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>253</v>
+        <v>99</v>
       </c>
       <c r="K59" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>317</v>
+        <v>263</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>318</v>
+        <v>120</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>150</v>
+        <v>295</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E60" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="K60" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>44</v>
+        <v>310</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>314</v>
+        <v>69</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E61" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>55</v>
+        <v>224</v>
       </c>
       <c r="K61" s="3">
         <v>30</v>
@@ -4513,280 +4565,562 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>323</v>
+        <v>162</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E62" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="K62" s="3">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E63" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="K63" s="3">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E64" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>189</v>
+        <v>324</v>
       </c>
       <c r="K64" s="3">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>211</v>
+        <v>139</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E65" s="3">
+        <v>6</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="K65" s="3">
         <v>3</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="K65" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>267</v>
+        <v>55</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E66" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="K66" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>341</v>
+        <v>69</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E67" s="3">
-        <v>0</v>
-      </c>
-      <c r="F67" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>296</v>
+      </c>
       <c r="G67" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>216</v>
+        <v>60</v>
       </c>
       <c r="K67" s="3">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>205</v>
+        <v>336</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E68" s="3">
-        <v>0</v>
-      </c>
-      <c r="F68" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>338</v>
+      </c>
       <c r="G68" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>67</v>
+        <v>252</v>
       </c>
       <c r="K68" s="3">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E69" s="3">
+        <v>4</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="K69" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" s="3">
+        <v>3</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K70" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B71" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C71" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E71" s="3">
+        <v>3</v>
+      </c>
+      <c r="F71" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="G71" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="K71" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="K72" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E73" s="3">
+        <v>3</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E74" s="3">
+        <v>3</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="K74" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E75" s="3">
+        <v>3</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D76" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E69" s="3">
+      <c r="E76" s="3">
         <v>0</v>
       </c>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="K69" s="3">
-        <v>1</v>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="K76" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E77" s="3">
+        <v>0</v>
+      </c>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="K77" s="3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K69"/>
+  <autoFilter ref="A1:K77"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4856,6 +5190,14 @@
     <hyperlink ref="I67" r:id="rId66"/>
     <hyperlink ref="I68" r:id="rId67"/>
     <hyperlink ref="I69" r:id="rId68"/>
+    <hyperlink ref="I70" r:id="rId69"/>
+    <hyperlink ref="I71" r:id="rId70"/>
+    <hyperlink ref="I72" r:id="rId71"/>
+    <hyperlink ref="I73" r:id="rId72"/>
+    <hyperlink ref="I74" r:id="rId73"/>
+    <hyperlink ref="I75" r:id="rId74"/>
+    <hyperlink ref="I76" r:id="rId75"/>
+    <hyperlink ref="I77" r:id="rId76"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4863,9 +5205,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -4874,211 +5216,259 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>200</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>160</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" s="3">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>202</v>
+        <v>70</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>203</v>
+        <v>71</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>226</v>
+        <v>76</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>227</v>
+        <v>77</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>228</v>
+        <v>79</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>229</v>
+        <v>80</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>238</v>
+        <v>119</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>239</v>
+        <v>120</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>240</v>
+        <v>122</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>241</v>
+        <v>123</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>279</v>
+        <v>124</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>280</v>
+        <v>125</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>268</v>
+        <v>126</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>281</v>
+        <v>127</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>334</v>
+        <v>133</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>335</v>
+        <v>138</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>324</v>
+        <v>140</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>336</v>
+        <v>141</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>267</v>
+        <v>183</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>337</v>
+        <v>184</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>315</v>
+        <v>185</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>338</v>
+        <v>186</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>343</v>
+        <v>263</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>205</v>
+        <v>120</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>307</v>
+      </c>
       <c r="F9" s="3" t="s">
-        <v>345</v>
+        <v>309</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="3">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G11"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -5088,6 +5478,8 @@
     <hyperlink ref="F7" r:id="rId6"/>
     <hyperlink ref="F8" r:id="rId7"/>
     <hyperlink ref="F9" r:id="rId8"/>
+    <hyperlink ref="F10" r:id="rId9"/>
+    <hyperlink ref="F11" r:id="rId10"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5102,178 +5494,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>351</v>
+        <v>370</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="B2" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="B3" s="3">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>358</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>319</v>
+        <v>219</v>
       </c>
       <c r="B7" s="3">
         <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>207</v>
+        <v>342</v>
       </c>
       <c r="B8" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="B11" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>328</v>
+        <v>388</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>371</v>
+        <v>391</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>202</v>
+        <v>392</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -5290,13 +5682,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2">
@@ -5304,10 +5696,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3">
@@ -5315,10 +5707,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4">
@@ -5326,10 +5718,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5">
@@ -5340,18 +5732,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="3">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>383</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -5369,51 +5750,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="D2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" s="3">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" s="3">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W26.xlsx
+++ b/reports/devops-juniors-israel-2026-W26.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="333">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-24T09:49:49</t>
+    <t xml:space="preserve">2026-06-25T09:40:12</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -163,15 +163,30 @@
     <t xml:space="preserve">2026-05-15</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
     <t xml:space="preserve">Linux System Administrator</t>
   </si>
   <si>
     <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
   </si>
   <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -181,946 +196,709 @@
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyager Labs</t>
+    <t xml:space="preserve">AI Inclined Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-inclined-systems-engineer-at-sb0-4429860196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataBank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallas,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Databases, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-technical-support-engineer-2-databank-1134066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Software Student, Annapurna Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-software-student-annapurna-labs-at-amazon-web-services-aws-4431605549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4432227642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4429863387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
   </si>
   <si>
     <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Inclined Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SB0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-inclined-systems-engineer-at-sb0-4429860196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Candex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-candex-4410031859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
+    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-specialist-at-log-on-software-4425797474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - JB-651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (35684)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-35684-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4432248548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategy Analyst Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (24892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4427354216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (Temporary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONE Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-one-technologies-4432205195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist - JB-594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-jb-594-at-pwc-israel-4429922813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4427419615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beth-El Industries Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician - junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
   </si>
   <si>
     <t xml:space="preserve">Technical Support Specialist</t>
   </si>
   <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-31</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4432227642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aristocrat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-aristocrat-4413900417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allied Worldwide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - JB-651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (35684)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-35684-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4432248548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-at-nebius-4425236974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk &amp; IT Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-it-administrator-at-mize-4425999700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strategy Analyst Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (24892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4427354216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Eng.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ultra Information Solutions</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4429856103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
   </si>
   <si>
     <t xml:space="preserve">Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-eng-at-ultra-information-solutions-4412395476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross River</t>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be2See.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-system-administrator-at-be2see-4429794206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4429852518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תומך/ת Help Desk וטכנאי/ת PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyber-Hive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%95%D7%9E%D7%9A-%D7%AA-help-desk%C2%A0%D7%95%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-pc-at-cyber-hive-4429851931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Operator</t>
   </si>
   <si>
     <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cross-river-4408813327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Algorithm System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/algorithm-system-engineer-at-elbit-systems-israel-4412906510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONE Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-one-technologies-4432205195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk / System</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egoz Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ayelet HaShahar, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-system-at-egoz-systems-4431679966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist - JB-594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-jb-594-at-pwc-israel-4429922813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (Temporary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4425818718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support – Power Quality Meters &amp; Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elspec Engineering ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-power-quality-meters-software-at-elspec-engineering-ltd-4413397801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4427419615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beth-El Industries Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician - junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4429856103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk - 239819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wobi Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-junior-at-wobi-ltd-4419670684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zoho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part time )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Operator</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-operator-at-tata-consultancy-services-4427424594</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4431366669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 2 Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tier-2-technician-at-solaredge-technologies-4431252112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סטודנט/ית למחלקת התכנון</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilever</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Safed, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%A1%D7%98%D7%95%D7%93%D7%A0%D7%98-%D7%99%D7%AA-%D7%9C%D7%9E%D7%97%D7%9C%D7%A7%D7%AA-%D7%94%D7%AA%D7%9B%D7%A0%D7%95%D7%9F-at-unilever-4426489234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Experience</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RG&amp;amp;T Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Dorado,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-no-experience-rgampt-solutions-1133829</t>
+    <t xml:space="preserve">System Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
   </si>
   <si>
     <t xml:space="preserve">Skill</t>
@@ -1135,19 +913,19 @@
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
     <t xml:space="preserve">Bash/Shell</t>
@@ -1156,16 +934,31 @@
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
@@ -1174,40 +967,22 @@
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kubernetes</t>
   </si>
   <si>
     <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1362,7 +1137,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>76</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
@@ -1370,7 +1145,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -1378,7 +1153,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -1386,7 +1161,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
@@ -1468,7 +1243,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>50</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22">
@@ -1484,7 +1259,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1492,7 +1267,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1510,7 +1285,7 @@
         <v>30</v>
       </c>
       <c r="B27" s="3">
-        <v>67</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28">
@@ -1538,7 +1313,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1626,7 +1401,7 @@
         <v>51</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1655,25 +1430,25 @@
         <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="3">
+        <v>100</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="3">
-        <v>88</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -1681,31 +1456,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F5" s="3">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -1713,31 +1488,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="3">
+        <v>74</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="3">
-        <v>76</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -1745,31 +1520,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="E7" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>74</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>75</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -1777,19 +1552,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" s="3">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>79</v>
@@ -1801,7 +1576,7 @@
         <v>80</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -1809,13 +1584,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>25</v>
@@ -1824,13 +1599,13 @@
         <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>48</v>
@@ -1841,31 +1616,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>86</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11">
@@ -1873,31 +1648,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F11" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12">
@@ -1911,25 +1686,25 @@
         <v>96</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -1943,25 +1718,25 @@
         <v>101</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>102</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>103</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14">
@@ -1969,31 +1744,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="D14" s="3" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -2001,22 +1776,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="3">
+        <v>32</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="3">
-        <v>44</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>30</v>
@@ -2039,25 +1814,25 @@
         <v>115</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>118</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -2065,31 +1840,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>121</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="3">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="18">
@@ -2103,25 +1878,25 @@
         <v>125</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>66</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19">
@@ -2129,31 +1904,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>69</v>
+        <v>132</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20">
@@ -2161,31 +1936,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21">
@@ -2193,31 +1968,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F21" s="3">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22">
@@ -2225,31 +2000,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23">
@@ -2257,31 +2032,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>63</v>
+        <v>152</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>118</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24">
@@ -2289,31 +2064,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F24" s="3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>155</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25">
@@ -2321,31 +2096,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>107</v>
+        <v>161</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F25" s="3">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26">
@@ -2353,31 +2128,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>63</v>
+        <v>167</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>48</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2430,7 +2205,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2445,22 +2220,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2">
@@ -2483,7 +2258,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
@@ -2495,7 +2270,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -2509,7 +2284,7 @@
         <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2518,7 +2293,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>30</v>
@@ -2530,7 +2305,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -2541,159 +2316,159 @@
         <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="3">
+        <v>100</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="3">
-        <v>88</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="K4" s="3">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="3">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="K5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3">
+        <v>74</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="G6" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="3">
-        <v>76</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="D7" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>75</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="K7" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E8" s="3">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>79</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>30</v>
@@ -2702,21 +2477,21 @@
         <v>80</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>25</v>
@@ -2725,92 +2500,92 @@
         <v>47</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K9" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>86</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K10" s="3">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E11" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="K11" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2821,31 +2596,31 @@
         <v>96</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="K12" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -2856,89 +2631,89 @@
         <v>101</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>102</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>103</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="K13" s="3">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="C14" s="3" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="K14" s="3">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="3">
+        <v>32</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="3">
-        <v>44</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="G15" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>30</v>
@@ -2950,7 +2725,7 @@
         <v>113</v>
       </c>
       <c r="K15" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -2961,66 +2736,66 @@
         <v>115</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="K16" s="3">
-        <v>35</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>121</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E17" s="3">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="K17" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -3031,273 +2806,273 @@
         <v>125</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>66</v>
+        <v>129</v>
       </c>
       <c r="K18" s="3">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>69</v>
+        <v>132</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K19" s="3">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="K20" s="3">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E21" s="3">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="K21" s="3">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="K22" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>63</v>
+        <v>152</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="K23" s="3">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E24" s="3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="K24" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>107</v>
+        <v>161</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E25" s="3">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="K25" s="3">
         <v>21</v>
@@ -3305,282 +3080,282 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>63</v>
+        <v>167</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="K26" s="3">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>107</v>
+        <v>177</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>155</v>
+        <v>48</v>
       </c>
       <c r="K27" s="3">
-        <v>6</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>91</v>
+        <v>182</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E28" s="3">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>118</v>
+        <v>59</v>
       </c>
       <c r="K28" s="3">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E29" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="K29" s="3">
         <v>31</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K29" s="3">
-        <v>40</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="3">
+        <v>13</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" s="3">
-        <v>20</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="G30" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>66</v>
+        <v>191</v>
       </c>
       <c r="K30" s="3">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>189</v>
+        <v>97</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="K31" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>192</v>
+        <v>95</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E32" s="3">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>196</v>
+        <v>70</v>
       </c>
       <c r="K32" s="3">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>202</v>
+        <v>59</v>
       </c>
       <c r="K33" s="3">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34">
@@ -3597,13 +3372,13 @@
         <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>206</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>30</v>
@@ -3612,33 +3387,33 @@
         <v>207</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>155</v>
+        <v>208</v>
       </c>
       <c r="K34" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>210</v>
+        <v>132</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>211</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>30</v>
@@ -3647,383 +3422,383 @@
         <v>212</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>48</v>
+        <v>213</v>
       </c>
       <c r="K35" s="3">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>119</v>
+        <v>214</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="3">
+        <v>10</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="3">
-        <v>16</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K36" s="3">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>218</v>
+        <v>146</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>189</v>
+        <v>62</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F37" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>220</v>
-      </c>
       <c r="J37" s="3" t="s">
-        <v>54</v>
+        <v>140</v>
       </c>
       <c r="K37" s="3">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>222</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K38" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>55</v>
+        <v>226</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>205</v>
+        <v>147</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E39" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>155</v>
+        <v>208</v>
       </c>
       <c r="K39" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>121</v>
+        <v>232</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E40" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>232</v>
+        <v>59</v>
       </c>
       <c r="K40" s="3">
-        <v>13</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>237</v>
+        <v>59</v>
       </c>
       <c r="K41" s="3">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E42" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>54</v>
+        <v>244</v>
       </c>
       <c r="K42" s="3">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>119</v>
+        <v>245</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>240</v>
+        <v>142</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>88</v>
+        <v>247</v>
       </c>
       <c r="K43" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>244</v>
+        <v>110</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>54</v>
+        <v>252</v>
       </c>
       <c r="K44" s="3">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>247</v>
+        <v>214</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>248</v>
+        <v>96</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>250</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>252</v>
+        <v>65</v>
       </c>
       <c r="K45" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>30</v>
@@ -4032,173 +3807,173 @@
         <v>256</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>257</v>
+        <v>188</v>
       </c>
       <c r="K46" s="3">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>259</v>
+        <v>142</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>260</v>
+        <v>126</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E47" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>261</v>
+        <v>237</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>146</v>
+        <v>191</v>
       </c>
       <c r="K47" s="3">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E48" s="3">
+        <v>6</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="K48" s="3">
         <v>10</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K48" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E49" s="3">
+        <v>4</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E49" s="3">
-        <v>10</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="J49" s="3" t="s">
-        <v>155</v>
+        <v>225</v>
       </c>
       <c r="K49" s="3">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="D50" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E50" s="3">
+        <v>4</v>
+      </c>
+      <c r="F50" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E50" s="3">
-        <v>10</v>
-      </c>
-      <c r="F50" s="3" t="s">
+      <c r="G50" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I50" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="G50" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I50" s="3" t="s">
+      <c r="J50" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="J50" s="3" t="s">
-        <v>274</v>
-      </c>
       <c r="K50" s="3">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>81</v>
+        <v>274</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>275</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E51" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>30</v>
@@ -4207,10 +3982,10 @@
         <v>276</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="K51" s="3">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -4221,19 +3996,19 @@
         <v>278</v>
       </c>
       <c r="C52" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E52" s="3">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E52" s="3">
-        <v>10</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="G52" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>30</v>
@@ -4242,112 +4017,112 @@
         <v>280</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="K52" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>281</v>
+        <v>43</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E53" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>224</v>
+        <v>59</v>
       </c>
       <c r="K53" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3</v>
+      </c>
+      <c r="F54" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="G54" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I54" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E54" s="3">
-        <v>8</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>288</v>
-      </c>
       <c r="J54" s="3" t="s">
-        <v>274</v>
+        <v>76</v>
       </c>
       <c r="K54" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E55" s="3">
+        <v>3</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E55" s="3">
-        <v>8</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>293</v>
-      </c>
       <c r="J55" s="3" t="s">
-        <v>54</v>
+        <v>188</v>
       </c>
       <c r="K55" s="3">
         <v>31</v>
@@ -4355,772 +4130,74 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>253</v>
+        <v>290</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>294</v>
+        <v>215</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E56" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>296</v>
+        <v>266</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>54</v>
+        <v>135</v>
       </c>
       <c r="K56" s="3">
-        <v>31</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>299</v>
+        <v>181</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>300</v>
+        <v>186</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E57" s="3">
-        <v>6</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>301</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>303</v>
+        <v>188</v>
       </c>
       <c r="K57" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E58" s="3">
-        <v>6</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="K58" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E59" s="3">
-        <v>6</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="K59" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E60" s="3">
-        <v>6</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E61" s="3">
-        <v>6</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="K61" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E62" s="3">
-        <v>6</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="K62" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E63" s="3">
-        <v>6</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="K63" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E64" s="3">
-        <v>6</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="K64" s="3">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E65" s="3">
-        <v>6</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="K65" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E66" s="3">
-        <v>6</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="K66" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E67" s="3">
-        <v>6</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="K67" s="3">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E68" s="3">
-        <v>4</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H68" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I68" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="K68" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E69" s="3">
-        <v>4</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="K69" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E70" s="3">
-        <v>3</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K70" s="3">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E71" s="3">
-        <v>3</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="J71" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="K71" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E72" s="3">
-        <v>3</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="K72" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E73" s="3">
-        <v>3</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="J73" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="K73" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E74" s="3">
-        <v>3</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="K74" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E75" s="3">
-        <v>3</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="J75" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="K75" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E76" s="3">
-        <v>0</v>
-      </c>
-      <c r="F76" s="3"/>
-      <c r="G76" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K76" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E77" s="3">
-        <v>0</v>
-      </c>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="J77" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="K77" s="3">
-        <v>2</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K77"/>
+  <autoFilter ref="A1:K57"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -5178,26 +4255,6 @@
     <hyperlink ref="I55" r:id="rId54"/>
     <hyperlink ref="I56" r:id="rId55"/>
     <hyperlink ref="I57" r:id="rId56"/>
-    <hyperlink ref="I58" r:id="rId57"/>
-    <hyperlink ref="I59" r:id="rId58"/>
-    <hyperlink ref="I60" r:id="rId59"/>
-    <hyperlink ref="I61" r:id="rId60"/>
-    <hyperlink ref="I62" r:id="rId61"/>
-    <hyperlink ref="I63" r:id="rId62"/>
-    <hyperlink ref="I64" r:id="rId63"/>
-    <hyperlink ref="I65" r:id="rId64"/>
-    <hyperlink ref="I66" r:id="rId65"/>
-    <hyperlink ref="I67" r:id="rId66"/>
-    <hyperlink ref="I68" r:id="rId67"/>
-    <hyperlink ref="I69" r:id="rId68"/>
-    <hyperlink ref="I70" r:id="rId69"/>
-    <hyperlink ref="I71" r:id="rId70"/>
-    <hyperlink ref="I72" r:id="rId71"/>
-    <hyperlink ref="I73" r:id="rId72"/>
-    <hyperlink ref="I74" r:id="rId73"/>
-    <hyperlink ref="I75" r:id="rId74"/>
-    <hyperlink ref="I76" r:id="rId75"/>
-    <hyperlink ref="I77" r:id="rId76"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5205,9 +4262,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="41" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -5228,10 +4285,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -5239,236 +4296,144 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" s="3">
+        <v>44</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>119</v>
+        <v>274</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>120</v>
+        <v>275</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D5" s="3">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>122</v>
+        <v>266</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>123</v>
+        <v>276</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>124</v>
+        <v>277</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>126</v>
+        <v>279</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>127</v>
+        <v>280</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>133</v>
+        <v>282</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>138</v>
+        <v>283</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>140</v>
+        <v>285</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>141</v>
+        <v>286</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="3">
-        <v>20</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="3">
-        <v>6</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="3">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="3">
-        <v>3</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G7"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -5476,10 +4441,6 @@
     <hyperlink ref="F5" r:id="rId4"/>
     <hyperlink ref="F6" r:id="rId5"/>
     <hyperlink ref="F7" r:id="rId6"/>
-    <hyperlink ref="F8" r:id="rId7"/>
-    <hyperlink ref="F9" r:id="rId8"/>
-    <hyperlink ref="F10" r:id="rId9"/>
-    <hyperlink ref="F11" r:id="rId10"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5494,178 +4455,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>369</v>
+        <v>295</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>370</v>
+        <v>296</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>371</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>338</v>
+        <v>266</v>
       </c>
       <c r="B2" s="3">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>372</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>373</v>
+        <v>279</v>
       </c>
       <c r="B3" s="3">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>374</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>375</v>
+        <v>285</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>376</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>348</v>
+        <v>301</v>
       </c>
       <c r="B5" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>377</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>378</v>
+        <v>183</v>
       </c>
       <c r="B6" s="3">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>379</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>219</v>
+        <v>304</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>380</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>342</v>
+        <v>306</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>381</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>382</v>
+        <v>308</v>
       </c>
       <c r="B9" s="3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>383</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>384</v>
+        <v>310</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>385</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>386</v>
+        <v>271</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>387</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>388</v>
+        <v>313</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>389</v>
+        <v>314</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>390</v>
+        <v>315</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>391</v>
+        <v>316</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>392</v>
+        <v>317</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>393</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>394</v>
+        <v>319</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>395</v>
+        <v>320</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>396</v>
+        <v>321</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>397</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -5685,10 +4646,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>398</v>
+        <v>323</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>399</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2">
@@ -5696,10 +4657,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>400</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3">
@@ -5710,7 +4671,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>401</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4">
@@ -5718,10 +4679,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>402</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5">
@@ -5729,10 +4690,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>403</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>
@@ -5753,13 +4714,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>404</v>
+        <v>329</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>405</v>
+        <v>330</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>406</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2">
@@ -5770,7 +4731,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>407</v>
+        <v>332</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5779,10 +4740,10 @@
         <v>30</v>
       </c>
       <c r="B3" s="3">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>407</v>
+        <v>332</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -5794,7 +4755,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>407</v>
+        <v>332</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W26.xlsx
+++ b/reports/devops-juniors-israel-2026-W26.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="315">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-25T09:40:12</t>
+    <t xml:space="preserve">2026-06-26T09:48:23</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -145,745 +145,703 @@
     <t xml:space="preserve">First Seen</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Inclined Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-inclined-systems-engineer-at-sb0-4429860196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataBank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallas,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Databases, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-technical-support-engineer-2-databank-1134066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4432227642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-compie-technologies-4433317648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-specialist-at-log-on-software-4425797474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - JB-651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support - Tier 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frontegg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Azure, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-at-frontegg-4421806900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-student-at-rapyd-4428700406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (35684)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-35684-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4432248548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategy Analyst Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (24892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4427354216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-at-abra-4432200564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist - JB-594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-jb-594-at-pwc-israel-4429922813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (Temporary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONE Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-one-technologies-4432205195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת Help Desk Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webox LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-help-desk-tier-1-at-webox-ltd-4430232360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpotNet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoham, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spotnet-4433071607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4427419615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beth-El Industries Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4429856103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Service Specialist - Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-service-specialist-tier-1-at-solaredge-technologies-4408365748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4429852518</t>
+  </si>
+  <si>
     <t xml:space="preserve">Developer Support Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Jfrog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Inclined Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SB0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-inclined-systems-engineer-at-sb0-4429860196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataBank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallas,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Databases, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-technical-support-engineer-2-databank-1134066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Software Student, Annapurna Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-software-student-annapurna-labs-at-amazon-web-services-aws-4431605549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4432227642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4429863387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-specialist-at-log-on-software-4425797474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - JB-651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (35684)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-35684-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4432248548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strategy Analyst Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (24892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4427354216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help Desk</t>
+    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תומך/ת Help Desk וטכנאי/ת PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyber-Hive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%95%D7%9E%D7%9A-%D7%AA-help-desk%C2%A0%D7%95%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-pc-at-cyber-hive-4429851931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
   </si>
   <si>
     <t xml:space="preserve">Genie</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (Temporary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONE Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-one-technologies-4432205195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist - JB-594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-jb-594-at-pwc-israel-4429922813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4427419615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beth-El Industries Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician - junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4429856103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be2See.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-system-administrator-at-be2see-4429794206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4429852518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">תומך/ת Help Desk וטכנאי/ת PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyber-Hive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%95%D7%9E%D7%9A-%D7%AA-help-desk%C2%A0%D7%95%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-pc-at-cyber-hive-4429851931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
   </si>
   <si>
     <t xml:space="preserve">Service Desk Operator</t>
@@ -895,12 +853,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-operator-at-tata-consultancy-services-4427424594</t>
   </si>
   <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
-  </si>
-  <si>
     <t xml:space="preserve">Skill</t>
   </si>
   <si>
@@ -910,28 +862,46 @@
     <t xml:space="preserve">What to learn / where to start</t>
   </si>
   <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">Linux</t>
@@ -940,49 +910,25 @@
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1137,7 +1083,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
@@ -1145,7 +1091,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1153,7 +1099,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -1161,7 +1107,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -1243,7 +1189,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
@@ -1251,7 +1197,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -1259,7 +1205,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1285,7 +1231,7 @@
         <v>30</v>
       </c>
       <c r="B27" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28">
@@ -1293,7 +1239,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -1369,7 +1315,7 @@
         <v>45</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1378,7 +1324,7 @@
         <v>46</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>47</v>
@@ -1401,10 +1347,10 @@
         <v>51</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>52</v>
@@ -1430,25 +1376,25 @@
         <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -1456,19 +1402,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F5" s="3">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>63</v>
@@ -1494,25 +1440,25 @@
         <v>67</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
@@ -1520,31 +1466,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="3">
+        <v>47</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="3">
-        <v>64</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -1552,31 +1498,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="3">
+        <v>44</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="3">
-        <v>57</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -1584,31 +1530,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="3">
+        <v>44</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="3">
-        <v>47</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -1616,31 +1562,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F10" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>87</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>88</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -1648,31 +1594,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="3">
+        <v>34</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="H11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="3">
-        <v>44</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12">
@@ -1680,31 +1626,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -1712,19 +1658,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>102</v>
@@ -1736,7 +1682,7 @@
         <v>103</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14">
@@ -1744,31 +1690,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>62</v>
+        <v>107</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -1776,31 +1722,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -1808,31 +1754,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17">
@@ -1840,31 +1786,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18">
@@ -1872,31 +1818,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="E18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="3">
         <v>26</v>
       </c>
-      <c r="F18" s="3">
-        <v>28</v>
-      </c>
       <c r="G18" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>129</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19">
@@ -1916,7 +1862,7 @@
         <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>133</v>
@@ -1928,7 +1874,7 @@
         <v>134</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20">
@@ -1936,31 +1882,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="3">
+        <v>23</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="3">
-        <v>27</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>140</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21">
@@ -1968,31 +1914,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="3">
+        <v>23</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F21" s="3">
-        <v>26</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="J21" s="3" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22">
@@ -2000,31 +1946,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="E22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="3">
+        <v>20</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F22" s="3">
-        <v>24</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>140</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23">
@@ -2032,31 +1978,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3">
         <v>20</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24">
@@ -2064,31 +2010,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="3">
+        <v>17</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F24" s="3">
-        <v>20</v>
-      </c>
-      <c r="G24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="25">
@@ -2096,31 +2042,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="E25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
         <v>17</v>
       </c>
       <c r="G25" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>164</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26">
@@ -2128,31 +2074,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="3">
+        <v>13</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="H26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="3">
-        <v>17</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2191,7 +2137,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2205,7 +2151,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2220,22 +2166,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2">
@@ -2249,7 +2195,7 @@
         <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2258,10 +2204,10 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>47</v>
@@ -2270,7 +2216,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -2284,16 +2230,16 @@
         <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E3" s="3">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>30</v>
@@ -2305,7 +2251,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2316,54 +2262,54 @@
         <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" s="3">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>63</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>30</v>
@@ -2375,7 +2321,7 @@
         <v>65</v>
       </c>
       <c r="K5" s="3">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -2386,264 +2332,264 @@
         <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="K6" s="3">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="3">
+        <v>47</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="3">
-        <v>64</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="K7" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="3">
+        <v>44</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="3">
-        <v>57</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K8" s="3">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="3">
+        <v>44</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="3">
-        <v>47</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K9" s="3">
-        <v>41</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>88</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="K10" s="3">
-        <v>37</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="3">
+        <v>34</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="3">
-        <v>44</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="K11" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="K12" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>102</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>30</v>
@@ -2652,7 +2598,7 @@
         <v>103</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -2660,177 +2606,177 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>62</v>
+        <v>107</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="K14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K15" s="3">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="K16" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K17" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="3">
         <v>26</v>
       </c>
-      <c r="E18" s="3">
-        <v>28</v>
-      </c>
       <c r="F18" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="K18" s="3">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
@@ -2847,13 +2793,13 @@
         <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>133</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>30</v>
@@ -2862,290 +2808,290 @@
         <v>134</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="K19" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="3">
+        <v>23</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="3">
-        <v>27</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="K20" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="3">
+        <v>23</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="3">
-        <v>26</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="J21" s="3" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="K21" s="3">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="D22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="3">
+        <v>20</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="3">
-        <v>24</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="K22" s="3">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E23" s="3">
         <v>20</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="K23" s="3">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="3">
+        <v>17</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="3">
-        <v>20</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="K24" s="3">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="D25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
         <v>17</v>
       </c>
       <c r="F25" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>164</v>
+        <v>125</v>
       </c>
       <c r="K25" s="3">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="3">
+        <v>13</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E26" s="3">
-        <v>17</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="K26" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>95</v>
+        <v>174</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="3">
+        <v>13</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="3">
-        <v>16</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K27" s="3">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28">
@@ -3153,10 +3099,10 @@
         <v>180</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>27</v>
@@ -3165,19 +3111,19 @@
         <v>13</v>
       </c>
       <c r="F28" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="J28" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="K28" s="3">
         <v>32</v>
@@ -3185,13 +3131,13 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>27</v>
@@ -3200,57 +3146,57 @@
         <v>13</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="K29" s="3">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="D30" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="K30" s="3">
-        <v>17</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31">
@@ -3258,57 +3204,57 @@
         <v>192</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="3">
+        <v>10</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="3">
-        <v>13</v>
-      </c>
-      <c r="F31" s="3" t="s">
+      <c r="G31" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="J31" s="3" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="K31" s="3">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>196</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>30</v>
@@ -3317,10 +3263,10 @@
         <v>197</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>70</v>
+        <v>167</v>
       </c>
       <c r="K32" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -3343,30 +3289,30 @@
         <v>201</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>202</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>59</v>
+        <v>203</v>
       </c>
       <c r="K33" s="3">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>205</v>
+        <v>117</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
@@ -3378,7 +3324,7 @@
         <v>206</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>30</v>
@@ -3387,21 +3333,21 @@
         <v>207</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>208</v>
+        <v>167</v>
       </c>
       <c r="K34" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>210</v>
-      </c>
       <c r="C35" s="3" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
@@ -3410,33 +3356,33 @@
         <v>10</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>213</v>
+        <v>104</v>
       </c>
       <c r="K35" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>214</v>
+        <v>105</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>62</v>
+        <v>212</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
@@ -3445,33 +3391,33 @@
         <v>10</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>213</v>
+        <v>104</v>
       </c>
       <c r="K36" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>146</v>
+        <v>215</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>62</v>
+        <v>216</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
@@ -3480,68 +3426,68 @@
         <v>10</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I37" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="J37" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="J37" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="K37" s="3">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E38" s="3">
+        <v>8</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="G38" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E38" s="3">
-        <v>10</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>224</v>
-      </c>
       <c r="J38" s="3" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="K38" s="3">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>147</v>
+        <v>225</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>26</v>
@@ -3550,68 +3496,68 @@
         <v>8</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="K39" s="3">
-        <v>10</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="3">
+        <v>6</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="G40" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E40" s="3">
-        <v>8</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>234</v>
-      </c>
       <c r="J40" s="3" t="s">
-        <v>59</v>
+        <v>179</v>
       </c>
       <c r="K40" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>235</v>
+        <v>85</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
@@ -3620,33 +3566,33 @@
         <v>6</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="K41" s="3">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>241</v>
+        <v>45</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
@@ -3655,33 +3601,33 @@
         <v>6</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="K42" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
@@ -3690,33 +3636,33 @@
         <v>6</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>247</v>
+        <v>186</v>
       </c>
       <c r="K43" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
@@ -3725,33 +3671,33 @@
         <v>6</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>252</v>
+        <v>203</v>
       </c>
       <c r="K44" s="3">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>96</v>
+        <v>245</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>236</v>
+        <v>132</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
@@ -3760,89 +3706,89 @@
         <v>6</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="K45" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>62</v>
+        <v>250</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E46" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="K46" s="3">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E47" s="3">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I47" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E47" s="3">
-        <v>6</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I47" s="3" t="s">
+      <c r="J47" s="3" t="s">
         <v>258</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>191</v>
       </c>
       <c r="K47" s="3">
         <v>17</v>
@@ -3856,19 +3802,19 @@
         <v>260</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E48" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>261</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>30</v>
@@ -3877,10 +3823,10 @@
         <v>262</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>208</v>
+        <v>60</v>
       </c>
       <c r="K48" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3888,150 +3834,150 @@
         <v>263</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E49" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>225</v>
+        <v>179</v>
       </c>
       <c r="K49" s="3">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E50" s="3">
+        <v>3</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I50" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E50" s="3">
-        <v>4</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>272</v>
-      </c>
       <c r="J50" s="3" t="s">
-        <v>273</v>
+        <v>60</v>
       </c>
       <c r="K50" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>62</v>
+        <v>132</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>76</v>
+        <v>183</v>
       </c>
       <c r="K51" s="3">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E52" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>76</v>
+        <v>237</v>
       </c>
       <c r="K52" s="3">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>43</v>
+        <v>276</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>264</v>
+        <v>196</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4040,164 +3986,26 @@
         <v>3</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="K53" s="3">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E54" s="3">
-        <v>3</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="K54" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E55" s="3">
-        <v>3</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="K55" s="3">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E56" s="3">
-        <v>3</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="K56" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="K57" s="3">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K57"/>
+  <autoFilter ref="A1:K53"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4251,10 +4059,6 @@
     <hyperlink ref="I51" r:id="rId50"/>
     <hyperlink ref="I52" r:id="rId51"/>
     <hyperlink ref="I53" r:id="rId52"/>
-    <hyperlink ref="I54" r:id="rId53"/>
-    <hyperlink ref="I55" r:id="rId54"/>
-    <hyperlink ref="I56" r:id="rId55"/>
-    <hyperlink ref="I57" r:id="rId56"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4262,11 +4066,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="41" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="1" max="1" width="33" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="5" max="5" width="43" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -4285,10 +4089,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -4296,151 +4100,127 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>266</v>
+        <v>206</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>276</v>
+        <v>210</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>277</v>
+        <v>105</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>278</v>
+        <v>211</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>279</v>
+        <v>201</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>280</v>
+        <v>213</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="3">
-        <v>3</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
     <hyperlink ref="F5" r:id="rId4"/>
     <hyperlink ref="F6" r:id="rId5"/>
-    <hyperlink ref="F7" r:id="rId6"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4455,178 +4235,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B2" s="3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="B3" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B4" s="3">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>285</v>
-      </c>
-      <c r="B4" s="3">
-        <v>19</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>301</v>
+        <v>267</v>
       </c>
       <c r="B5" s="3">
         <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>183</v>
+        <v>287</v>
       </c>
       <c r="B6" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>304</v>
+        <v>177</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>306</v>
+        <v>274</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>308</v>
+        <v>256</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="B12" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="B13" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>321</v>
+        <v>165</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -4646,10 +4426,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2">
@@ -4657,10 +4437,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
     </row>
     <row r="3">
@@ -4668,10 +4448,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4">
@@ -4679,10 +4459,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5">
@@ -4693,7 +4473,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -4714,13 +4494,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2">
@@ -4728,10 +4508,10 @@
         <v>31</v>
       </c>
       <c r="B2" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4740,10 +4520,10 @@
         <v>30</v>
       </c>
       <c r="B3" s="3">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -4755,7 +4535,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W26.xlsx
+++ b/reports/devops-juniors-israel-2026-W26.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="388">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-26T09:48:23</t>
+    <t xml:space="preserve">2026-06-28T09:28:15</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -163,6 +163,24 @@
     <t xml:space="preserve">2026-06-02</t>
   </si>
   <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
     <t xml:space="preserve">AI Inclined Systems Engineer</t>
   </si>
   <si>
@@ -181,751 +199,952 @@
     <t xml:space="preserve">2026-06-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Engineer 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataBank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallas,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Databases, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-technical-support-engineer-2-databank-1134066</t>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4432227642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4429863387</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-25</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-specialist-at-log-on-software-4425797474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allied Worldwide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - JB-651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-student-at-rapyd-4428700406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (35684)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-35684-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4434276396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategy Analyst Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (24892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4427354216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-01</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist - JB-594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-jb-594-at-pwc-israel-4429922813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONE Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-one-technologies-4432205195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (Temporary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת Help Desk Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webox LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-help-desk-tier-1-at-webox-ltd-4430232360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpotNet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoham, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spotnet-4433071607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support – Power Quality Meters &amp; Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elspec Engineering ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-power-quality-meters-software-at-elspec-engineering-ltd-4413397801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4427419615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Administrator (36014)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-36014-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4434285138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beth-El Industries Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wobi Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-junior-at-wobi-ltd-4419670684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician - junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4429856103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-14</t>
   </si>
   <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4432227642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
+    <t xml:space="preserve">Multimedia Systems &amp; IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deloitte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/multimedia-systems-it-support-specialist-at-deloitte-4433302126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part time )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4429852518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-south-apac-sea-anz-ind-subcont-4427828397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aeronautical Information Service Cadet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grenada Airports Authority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">St. George's,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-aeronautical-information-service-cadet-grenada-airports-authority-1134169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-operator-at-tata-consultancy-services-4427424594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תומך/ת Help Desk וטכנאי/ת PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyber-Hive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%95%D7%9E%D7%9A-%D7%AA-help-desk%C2%A0%D7%95%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-pc-at-cyber-hive-4429851931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
   </si>
   <si>
     <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-compie-technologies-4433317648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-specialist-at-log-on-software-4425797474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - JB-651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support - Tier 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frontegg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Azure, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-at-frontegg-4421806900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-student-at-rapyd-4428700406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (35684)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-35684-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4432248548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strategy Analyst Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (24892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4427354216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4431366669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist (28516)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-28516-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4434281333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Support &amp; Systems Operations Specialist- position no. 1601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBI Investment House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-support-systems-operations-specialist-position-no-1601-at-ibi-investment-house-4423609880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Support Technician Helpdesk Offboardings &amp;amp; Access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pixel Machinery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">California, California, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-customer-support-technician-helpdesk-offboardings-amp-access-pixel-machinery-1134154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Test Student (Mechanical Engineering)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-test-student-mechanical-engineering-at-landa-4434264750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scheduling Coordinator Entry Level No Experience Needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travel Planning Professionals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New York, New York, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-scheduling-coordinator-entry-level-no-experience-needed-travel-planning-professionals-1134108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
   </si>
   <si>
     <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-at-abra-4432200564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist - JB-594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-jb-594-at-pwc-israel-4429922813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (Temporary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONE Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-one-technologies-4432205195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/אשת Help Desk Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Webox LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-help-desk-tier-1-at-webox-ltd-4430232360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpotNet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spotnet-4433071607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4427419615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beth-El Industries Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4429856103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Service Specialist - Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-service-specialist-tier-1-at-solaredge-technologies-4408365748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zoho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4429852518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">תומך/ת Help Desk וטכנאי/ת PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyber-Hive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%95%D7%9E%D7%9A-%D7%AA-help-desk%C2%A0%D7%95%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-pc-at-cyber-hive-4429851931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-operator-at-tata-consultancy-services-4427424594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
   </si>
   <si>
     <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
@@ -1083,7 +1302,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>52</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -1091,7 +1310,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -1099,7 +1318,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -1107,7 +1326,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>331</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10">
@@ -1189,7 +1408,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
@@ -1197,7 +1416,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -1205,7 +1424,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -1231,7 +1450,7 @@
         <v>30</v>
       </c>
       <c r="B27" s="3">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28">
@@ -1247,7 +1466,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1347,10 +1566,10 @@
         <v>51</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3" s="3">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>52</v>
@@ -1379,16 +1598,16 @@
         <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>58</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>59</v>
@@ -1408,25 +1627,25 @@
         <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -1434,7 +1653,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>67</v>
@@ -1443,22 +1662,22 @@
         <v>68</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -1466,31 +1685,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>71</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F7" s="3">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
@@ -1498,31 +1717,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" s="3">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
@@ -1530,31 +1749,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>80</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F9" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
@@ -1568,25 +1787,25 @@
         <v>85</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F10" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -1600,25 +1819,25 @@
         <v>90</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F11" s="3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12">
@@ -1626,19 +1845,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>96</v>
@@ -1670,7 +1889,7 @@
         <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>102</v>
@@ -1682,7 +1901,7 @@
         <v>103</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -1690,31 +1909,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="3">
+        <v>36</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="3">
-        <v>30</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -1722,31 +1941,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="3">
+        <v>34</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" s="3">
-        <v>28</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
@@ -1754,31 +1973,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="3">
+        <v>30</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="3">
-        <v>28</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="17">
@@ -1786,31 +2005,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="E17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="3">
+        <v>28</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="3">
-        <v>27</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18">
@@ -1818,31 +2037,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="3">
+        <v>28</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="3">
-        <v>26</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="19">
@@ -1850,31 +2069,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="3">
+        <v>27</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="H19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" s="3">
-        <v>24</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20">
@@ -1882,31 +2101,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="3">
+        <v>27</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="3">
-        <v>23</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="21">
@@ -1914,31 +2133,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="3">
+        <v>26</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="3">
-        <v>23</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="J21" s="3" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22">
@@ -1946,31 +2165,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="3">
+        <v>24</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="H22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="3">
-        <v>20</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23">
@@ -1978,31 +2197,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F23" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24">
@@ -2010,31 +2229,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="3">
+        <v>23</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" s="3">
-        <v>17</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="25">
@@ -2042,31 +2261,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>125</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26">
@@ -2074,31 +2293,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>164</v>
+        <v>121</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>167</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2137,7 +2356,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2151,7 +2370,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2166,22 +2385,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2">
@@ -2204,7 +2423,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>30</v>
@@ -2216,7 +2435,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -2230,16 +2449,16 @@
         <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E3" s="3">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>30</v>
@@ -2251,7 +2470,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -2265,19 +2484,19 @@
         <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>59</v>
@@ -2286,7 +2505,7 @@
         <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -2297,36 +2516,36 @@
         <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E5" s="3">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K5" s="3">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>67</v>
@@ -2335,133 +2554,133 @@
         <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" s="3">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K6" s="3">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>71</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E7" s="3">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K7" s="3">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E8" s="3">
+        <v>57</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K8" s="3">
         <v>44</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="K8" s="3">
-        <v>38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>80</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E9" s="3">
+        <v>47</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K9" s="3">
         <v>44</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="K9" s="3">
-        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -2472,31 +2691,31 @@
         <v>85</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="3">
+        <v>44</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K10" s="3">
         <v>40</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K10" s="3">
-        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -2507,54 +2726,54 @@
         <v>90</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E11" s="3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="K11" s="3">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>96</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>30</v>
@@ -2566,7 +2785,7 @@
         <v>98</v>
       </c>
       <c r="K12" s="3">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -2583,13 +2802,13 @@
         <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>102</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>30</v>
@@ -2598,756 +2817,756 @@
         <v>103</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="K13" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="3">
+        <v>36</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="G14" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="3">
-        <v>30</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="K14" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="3">
+        <v>34</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="3">
-        <v>28</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="K15" s="3">
-        <v>37</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="D16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="3">
+        <v>30</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="3">
+      <c r="J16" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K16" s="3">
         <v>28</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K16" s="3">
-        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="D17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="3">
+        <v>28</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="3">
-        <v>27</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="K17" s="3">
-        <v>8</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="3">
+        <v>28</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="3">
-        <v>26</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="K18" s="3">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="3">
+        <v>27</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="G19" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="3">
-        <v>24</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="K19" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="3">
+        <v>27</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="G20" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="3">
-        <v>23</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="3">
+        <v>26</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="3">
-        <v>23</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="J21" s="3" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="K21" s="3">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="3">
+        <v>24</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="3">
-        <v>20</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="K22" s="3">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E23" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="K23" s="3">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="3">
+        <v>23</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="3">
-        <v>17</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="K24" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="K25" s="3">
-        <v>8</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>164</v>
+        <v>121</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>167</v>
+        <v>66</v>
       </c>
       <c r="K26" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E27" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G27" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="J27" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>179</v>
-      </c>
       <c r="K27" s="3">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>175</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>177</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>183</v>
+        <v>74</v>
       </c>
       <c r="K28" s="3">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>184</v>
+        <v>99</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" s="3">
+        <v>16</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" s="3">
-        <v>13</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="G29" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="K29" s="3">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="3">
+        <v>13</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="J30" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E30" s="3">
-        <v>10</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>179</v>
-      </c>
       <c r="K30" s="3">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="3">
+        <v>13</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="J31" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="3">
-        <v>10</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="K31" s="3">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" s="3">
+        <v>13</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="3">
-        <v>10</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="K32" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="3">
+        <v>13</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E33" s="3">
+      <c r="J33" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K33" s="3">
         <v>10</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="K33" s="3">
-        <v>11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>204</v>
+        <v>99</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E34" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="K34" s="3">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>107</v>
+        <v>204</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
@@ -3356,33 +3575,33 @@
         <v>10</v>
       </c>
       <c r="F35" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>210</v>
-      </c>
       <c r="J35" s="3" t="s">
-        <v>104</v>
+        <v>188</v>
       </c>
       <c r="K35" s="3">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>212</v>
+        <v>57</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
@@ -3391,33 +3610,33 @@
         <v>10</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>104</v>
+        <v>211</v>
       </c>
       <c r="K36" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>215</v>
+        <v>143</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>216</v>
+        <v>57</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
@@ -3426,150 +3645,150 @@
         <v>10</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>219</v>
+        <v>74</v>
       </c>
       <c r="K37" s="3">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>99</v>
+        <v>214</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>132</v>
+        <v>216</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="K38" s="3">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="3">
+        <v>10</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E39" s="3">
-        <v>8</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>227</v>
-      </c>
       <c r="J39" s="3" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="K39" s="3">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="3">
+        <v>10</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="J40" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E40" s="3">
-        <v>6</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>179</v>
-      </c>
       <c r="K40" s="3">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>85</v>
+        <v>231</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>30</v>
@@ -3578,7 +3797,7 @@
         <v>233</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>54</v>
+        <v>152</v>
       </c>
       <c r="K41" s="3">
         <v>2</v>
@@ -3586,349 +3805,349 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="C42" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="3">
+        <v>10</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E42" s="3">
-        <v>6</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>236</v>
-      </c>
       <c r="J42" s="3" t="s">
-        <v>237</v>
+        <v>188</v>
       </c>
       <c r="K42" s="3">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" s="3">
+        <v>10</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E43" s="3">
-        <v>6</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>239</v>
-      </c>
       <c r="J43" s="3" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="K43" s="3">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>243</v>
-      </c>
       <c r="J44" s="3" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="K44" s="3">
-        <v>11</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E45" s="3">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="G45" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I45" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E45" s="3">
-        <v>6</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="J45" s="3" t="s">
-        <v>83</v>
+        <v>229</v>
       </c>
       <c r="K45" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>249</v>
+        <v>159</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>250</v>
+        <v>121</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E46" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>219</v>
+        <v>66</v>
       </c>
       <c r="K46" s="3">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E47" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>258</v>
+        <v>188</v>
       </c>
       <c r="K47" s="3">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>260</v>
+        <v>139</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E48" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>60</v>
+        <v>195</v>
       </c>
       <c r="K48" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E49" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="K49" s="3">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>164</v>
+        <v>121</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>60</v>
+        <v>229</v>
       </c>
       <c r="K50" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E51" s="3">
+        <v>6</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="J51" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E51" s="3">
-        <v>3</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>183</v>
       </c>
       <c r="K51" s="3">
         <v>32</v>
@@ -3936,76 +4155,805 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E52" s="3">
+        <v>6</v>
+      </c>
+      <c r="F52" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="G52" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I52" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E52" s="3">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>275</v>
-      </c>
       <c r="J52" s="3" t="s">
-        <v>237</v>
+        <v>60</v>
       </c>
       <c r="K52" s="3">
-        <v>31</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E53" s="3">
+        <v>6</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="K53" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C53" s="3" t="s">
+      <c r="C54" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E54" s="3">
+        <v>6</v>
+      </c>
+      <c r="F54" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E53" s="3">
+      <c r="G54" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="K54" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E55" s="3">
+        <v>6</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K55" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E56" s="3">
+        <v>6</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K56" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="K57" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E58" s="3">
+        <v>4</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="K58" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E59" s="3">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K59" s="3">
         <v>3</v>
       </c>
-      <c r="F53" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="G53" s="3" t="s">
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="K60" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E61" s="3">
+        <v>4</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="K62" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E63" s="3">
+        <v>3</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="K63" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E64" s="3">
+        <v>3</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K64" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E65" s="3">
+        <v>3</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="K65" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K66" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" s="3">
+        <v>3</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K67" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" s="3">
+        <v>3</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E69" s="3">
+        <v>3</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="J69" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H53" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K53" s="3">
-        <v>10</v>
+      <c r="K69" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" s="3">
+        <v>3</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="K70" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E71" s="3">
+        <v>3</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E72" s="3">
+        <v>0</v>
+      </c>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E73" s="3">
+        <v>0</v>
+      </c>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K73" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" s="3">
+        <v>0</v>
+      </c>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K74" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K53"/>
+  <autoFilter ref="A1:K74"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4059,6 +5007,27 @@
     <hyperlink ref="I51" r:id="rId50"/>
     <hyperlink ref="I52" r:id="rId51"/>
     <hyperlink ref="I53" r:id="rId52"/>
+    <hyperlink ref="I54" r:id="rId53"/>
+    <hyperlink ref="I55" r:id="rId54"/>
+    <hyperlink ref="I56" r:id="rId55"/>
+    <hyperlink ref="I57" r:id="rId56"/>
+    <hyperlink ref="I58" r:id="rId57"/>
+    <hyperlink ref="I59" r:id="rId58"/>
+    <hyperlink ref="I60" r:id="rId59"/>
+    <hyperlink ref="I61" r:id="rId60"/>
+    <hyperlink ref="I62" r:id="rId61"/>
+    <hyperlink ref="I63" r:id="rId62"/>
+    <hyperlink ref="I64" r:id="rId63"/>
+    <hyperlink ref="I65" r:id="rId64"/>
+    <hyperlink ref="I66" r:id="rId65"/>
+    <hyperlink ref="I67" r:id="rId66"/>
+    <hyperlink ref="I68" r:id="rId67"/>
+    <hyperlink ref="I69" r:id="rId68"/>
+    <hyperlink ref="I70" r:id="rId69"/>
+    <hyperlink ref="I71" r:id="rId70"/>
+    <hyperlink ref="I72" r:id="rId71"/>
+    <hyperlink ref="I73" r:id="rId72"/>
+    <hyperlink ref="I74" r:id="rId73"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4066,11 +5035,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="33" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="43" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -4089,10 +5058,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -4100,127 +5069,243 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>136</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" s="3">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>137</v>
+        <v>64</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>138</v>
+        <v>69</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>209</v>
+        <v>159</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>206</v>
+        <v>247</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>210</v>
+        <v>248</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>105</v>
+        <v>280</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>211</v>
+        <v>281</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>201</v>
+        <v>252</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>213</v>
+        <v>282</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>104</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="3">
+        <v>4</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G11"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
     <hyperlink ref="F5" r:id="rId4"/>
     <hyperlink ref="F6" r:id="rId5"/>
+    <hyperlink ref="F7" r:id="rId6"/>
+    <hyperlink ref="F8" r:id="rId7"/>
+    <hyperlink ref="F9" r:id="rId8"/>
+    <hyperlink ref="F10" r:id="rId9"/>
+    <hyperlink ref="F11" r:id="rId10"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4235,178 +5320,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>279</v>
+        <v>352</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>280</v>
+        <v>353</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>281</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>261</v>
+        <v>289</v>
       </c>
       <c r="B2" s="3">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>282</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>251</v>
+        <v>299</v>
       </c>
       <c r="B3" s="3">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>283</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>284</v>
+        <v>357</v>
       </c>
       <c r="B4" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>285</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>267</v>
+        <v>318</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>286</v>
+        <v>359</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>288</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>177</v>
+        <v>307</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>289</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>274</v>
+        <v>186</v>
       </c>
       <c r="B8" s="3">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>290</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>256</v>
+        <v>363</v>
       </c>
       <c r="B9" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>291</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>292</v>
+        <v>365</v>
       </c>
       <c r="B10" s="3">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>293</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="B11" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>295</v>
+        <v>367</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>296</v>
+        <v>368</v>
       </c>
       <c r="B12" s="3">
         <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>297</v>
+        <v>369</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>298</v>
+        <v>370</v>
       </c>
       <c r="B13" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>299</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>300</v>
+        <v>372</v>
       </c>
       <c r="B14" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>301</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>302</v>
+        <v>374</v>
       </c>
       <c r="B15" s="3">
         <v>3</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>303</v>
+        <v>375</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>165</v>
+        <v>376</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>304</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -4426,10 +5511,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>305</v>
+        <v>378</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>306</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2">
@@ -4437,10 +5522,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>307</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3">
@@ -4448,10 +5533,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>308</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4">
@@ -4459,10 +5544,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>309</v>
+        <v>382</v>
       </c>
     </row>
     <row r="5">
@@ -4473,7 +5558,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>310</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -4494,13 +5579,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>311</v>
+        <v>384</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>312</v>
+        <v>385</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>313</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2">
@@ -4511,7 +5596,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>314</v>
+        <v>387</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4520,10 +5605,10 @@
         <v>30</v>
       </c>
       <c r="B3" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>314</v>
+        <v>387</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -4532,10 +5617,10 @@
         <v>32</v>
       </c>
       <c r="B4" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>314</v>
+        <v>387</v>
       </c>
       <c r="D4" s="3"/>
     </row>
